--- a/Assessment Questions/AIE/BIA - 119/Connecting to Various Data Sources_/Extracting Characters/Extracting Characters.xlsx
+++ b/Assessment Questions/AIE/BIA - 119/Connecting to Various Data Sources_/Extracting Characters/Extracting Characters.xlsx
@@ -1,180 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
-  <si>
-    <t>Row_ID,Product_Code,Order_Reference,Email_Address,Phone_Number,Product_Name,Address_Full,Date_Time_Stamp,File_Path,URL,ID_Number,Serial_Number,Transaction_Code</t>
-  </si>
-  <si>
-    <t>1,PRD-001-2024,ORD-1001-USA,john.smith@email.com,(555) 123-4567,MacBook Pro 16-inch,123 Main Street, Chicago IL 60601,2024-01-05 14:30:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/macbook-pro,ID-12345-ABCD,S/N:MPR-2024-001,TRX|2024|01|001</t>
-  </si>
-  <si>
-    <t>2,PRD-002-2024,ORD-1002-USA,jane.doe@company.com,(555) 234-5678,Magic Mouse Wireless,456 Oak Avenue, Boston MA 02101,2024-01-05 14:35:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/magic-mouse,ID-12346-EFGH,S/N:MMW-2024-002,TRX|2024|01|002</t>
-  </si>
-  <si>
-    <t>3,PRD-003-2024,ORD-1003-CAN,robert.wilson@email.ca,(555) 345-6789,Designer Jeans Blue,789 Pine Street, Toronto ON M5V 2T6,2024-01-06 09:15:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/designer-jeans,ID-12347-IJKL,S/N:DJB-2024-003,TRX|2024|01|003</t>
-  </si>
-  <si>
-    <t>4,PRD-004-2024,ORD-1004-USA,sarah.johnson@email.com,(555) 456-7890,27-inch 4K Monitor,321 Elm Street, Austin TX 78701,2024-01-06 10:45:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/4k-monitor,ID-12348-MNOP,S/N:4KM-2024-004,TRX|2024|01|004</t>
-  </si>
-  <si>
-    <t>5,PRD-005-2024,ORD-1005-UK,michael.brown@email.co.uk,44-20-7946-0123,Executive Leather Chair,654 Maple Avenue, London EC1A 1BB,2024-01-07 11:20:00,D:\Reports\2024\Q1\February\sales.csv,https://www.example.com/products/executive-chair,ID-12349-QRST,S/N:ELC-2024-005,TRX|2024|02|001</t>
-  </si>
-  <si>
-    <t>6,PRD-006-2024,ORD-1006-AUS,emily.davis@email.com.au,61-2-9876-5432,Mechanical RGB Keyboard,987 Cedar Lane, Sydney NSW 2000,2024-01-07 13:00:00,D:\Reports\2024\Q1\February\sales.csv,https://www.example.com/products/mechanical-keyboard,ID-12350-UVWX,S/N:MRK-2024-006,TRX|2024|02|002</t>
-  </si>
-  <si>
-    <t>7,PRD-007-2024,ORD-1007-USA,lisa.anderson@email.com,555-987-6543,Leather Jacket Black,147 Birch Street, Los Angeles CA 90001,2024-01-08 08:45:00,D:\Reports\2024\Q1\February\sales.csv,https://www.example.com/products/leather-jacket,ID-12351-YZAB,S/N:LJB-2024-007,TRX|2024|02|003</t>
-  </si>
-  <si>
-    <t>8,PRD-008-2024,ORD-1008-GER,robert.taylor@email.de,49-30-12345678,iPad Pro 12.9-inch,258 Spruce Avenue, Berlin 10115,2024-01-08 09:30:00,E:\Data\2024\March\products.csv,https://www.example.com/products/ipad-pro,ID-12352-CDEF,S/N:IPP-2024-008,TRX|2024|03|001</t>
-  </si>
-  <si>
-    <t>9,PRD-009-2024,ORD-1009-FRA,jennifer.martinez@email.fr,33-1-45678901,Floor Lamp Modern,369 Walnut Street, Paris 75001,2024-01-09 10:15:00,E:\Data\2024\March\products.csv,https://www.example.com/products/floor-lamp,ID-12353-GHIJ,S/N:FLM-2024-009,TRX|2024|03|002</t>
-  </si>
-  <si>
-    <t>10,PRD-010-2024,ORD-1010-USA,william.brown@email.com,555-321-0987,Running Shoes Pro,741 Cherry Lane, Detroit MI 48201,2024-01-09 14:20:00,E:\Data\2024\March\products.csv,https://www.example.com/products/running-shoes,ID-12354-KLMN,S/N:RSP-2024-010,TRX|2024|03|003</t>
-  </si>
-  <si>
-    <t>11,PRD-011-2024,ORD-1011-CAN,patricia.davis@email.ca,416-555-1234,Gaming Laptop RTX,852 Dogwood Drive, Vancouver BC V6B 4Y8,2024-01-10 11:00:00,F:\Sales\2024\April\transactions.csv,https://www.example.com/products/gaming-laptop,ID-12355-OPQR,S/N:GLP-2024-011,TRX|2024|04|001</t>
-  </si>
-  <si>
-    <t>12,PRD-012-2024,ORD-1012-UK,michael.miller@email.co.uk,44-141-555-6789,Wireless Noise Cancelling Headphones,951 Fir Lane, Manchester M1 1AE,2024-01-10 15:30:00,F:\Sales\2024\April\transactions.csv,https://www.example.com/products/headphones,ID-12356-STUV,S/N:WNC-2024-012,TRX|2024|04|002</t>
-  </si>
-  <si>
-    <t>13,PRD-013-2024,ORD-1013-USA,jessica.thomas@email.com,555-789-0123,Wool Winter Coat,753 Poplar Avenue, San Diego CA 92101,2024-01-11 09:45:00,F:\Sales\2024\April\transactions.csv,https://www.example.com/products/wool-coat,ID-12357-WXYZ,S/N:WWC-2024-013,TRX|2024|04|003</t>
-  </si>
-  <si>
-    <t>14,PRD-014-2024,ORD-1014-AUS,richard.moore@email.com.au,61-3-9876-5432,5-Tier Oak Bookshelf,159 Cypress Court, Melbourne VIC 3000,2024-01-11 12:15:00,G:\Data\2024\May\orders.csv,https://www.example.com/products/bookshelf,ID-12358-ABCD,S/N:BOO-2024-014,TRX|2024|05|001</t>
-  </si>
-  <si>
-    <t>15,PRD-015-2024,ORD-1015-GER,susan.taylor@email.de,49-89-1234567,Smartphone Pro Max,357 Willow Drive, Munich 80331,2024-01-12 10:00:00,G:\Data\2024\May\orders.csv,https://www.example.com/products/smartphone,ID-12359-EFGH,S/N:SPM-2024-015,TRX|2024|05|002</t>
-  </si>
-  <si>
-    <t>16,PRD-016-2024,ORD-1016-FRA,thomas.anderson@email.fr,33-4-98765432,Dress Shirt Formal White,951 Magnolia Road, Lyon 69001,2024-01-12 13:45:00,G:\Data\2024\May\orders.csv,https://www.example.com/products/dress-shirt,ID-12360-IJKL,S/N:DSF-2024-016,TRX|2024|05|003</t>
-  </si>
-  <si>
-    <t>17,PRD-017-2024,ORD-1017-USA,charles.jackson@email.com,555-456-7890,External SSD 1TB,753 Ash Street, Portland OR 97201,2024-01-13 08:30:00,H:\Reports\2024\June\inventory.csv,https://www.example.com/products/external-ssd,ID-12361-MNOP,S/N:ESS-2024-017,TRX|2024|06|001</t>
-  </si>
-  <si>
-    <t>18,PRD-018-2024,ORD-1018-CAN,sarah.white@email.ca,604-555-6789,Cotton Hoodie Gray,159 Beech Court, Calgary AB T2P 1J9,2024-01-13 16:20:00,H:\Reports\2024\June\inventory.csv,https://www.example.com/products/hoodie,ID-12362-QRST,S/N:CHG-2024-018,TRX|2024|06|002</t>
-  </si>
-  <si>
-    <t>19,PRD-019-2024,ORD-1019-UK,james.walker@email.co.uk,44-161-555-1234,Gaming Desk RGB,357 Cedar Avenue, Birmingham B1 1BB,2024-01-14 11:30:00,H:\Reports\2024\June\inventory.csv,https://www.example.com/products/gaming-desk,ID-12363-UVWX,S/N:GDR-2024-019,TRX|2024|06|003</t>
-  </si>
-  <si>
-    <t>20,PRD-020-2024,ORD-1020-USA,betty.hall@email.com,555-234-5678,4K Webcam Pro,753 Palm Avenue, Seattle WA 98101,2024-01-14 14:15:00,I:\Data\2024\July\products.csv,https://www.example.com/products/webcam,ID-12364-YZAB,S/N:4KW-2024-020,TRX|2024|07|001</t>
-  </si>
-  <si>
-    <t>21,PRD-021-2024,ORD-1021-AUS,kevin.young@email.com.au,61-7-5555-1234,Thunderbolt Docking Station,951 Elm Drive, Brisbane QLD 4000,2024-02-01 09:00:00,I:\Data\2024\July\products.csv,https://www.example.com/products/docking-station,ID-12365-CDEF,S/N:TDS-2024-021,TRX|2024|07|002</t>
-  </si>
-  <si>
-    <t>22,PRD-022-2024,ORD-1022-GER,nancy.allen@email.de,49-40-1234567,Winter Parka Black,753 Oak Court, Hamburg 20095,2024-02-01 10:45:00,I:\Data\2024\July\products.csv,https://www.example.com/products/winter-parka,ID-12366-GHIJ,S/N:WPB-2024-022,TRX|2024|07|003</t>
-  </si>
-  <si>
-    <t>23,PRD-023-2024,ORD-1023-FRA,edward.king@email.fr,33-5-98765432,Office Desk Walnut,159 Pine Street, Toulouse 31000,2024-02-02 13:30:00,J:\Sales\2024\August\transactions.csv,https://www.example.com/products/office-desk,ID-12367-KLMN,S/N:ODW-2024-023,TRX|2024|08|001</t>
-  </si>
-  <si>
-    <t>24,PRD-024-2024,ORD-1024-USA,donna.wright@email.com,555-876-5432,USB-C Hub 7-in-1,357 Spruce Lane, Denver CO 80201,2024-02-02 15:20:00,J:\Sales\2024\August\transactions.csv,https://www.example.com/products/usb-hub,ID-12368-OPQR,S/N:UCH-2024-024,TRX|2024|08|002</t>
-  </si>
-  <si>
-    <t>25,PRD-025-2024,ORD-1025-CAN,george.lopez@email.ca,403-555-9876,Casual Blazer Navy,951 Walnut Avenue, Edmonton AB T5J 0A9,2024-02-03 08:15:00,J:\Sales\2024\August\transactions.csv,https://www.example.com/products/casual-blazer,ID-12369-STUV,S/N:CBN-2024-025,TRX|2024|08|003</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Extraction_Type,Steps_to_Perform,Expected_Result,Use_Case</t>
-  </si>
-  <si>
-    <t>1,"Extract the first 3 characters from 'Product_Code' column into a new column named 'Product_Prefix'. What is the prefix for the first product?","First Characters","Add Column → Extract → First Characters → Count: 3 → New column: Product_Prefix","PRD (for PRD-001-2024)","Identifying product category codes, extracting prefixes"</t>
-  </si>
-  <si>
-    <t>2,"Extract the last 4 characters from 'Product_Code' column into a new column named 'Product_Year'. What is the year for the first product?","Last Characters","Add Column → Extract → Last Characters → Count: 4 → New column: Product_Year","2024","Extracting year from codes, getting suffixes"</t>
-  </si>
-  <si>
-    <t>3,"Extract the middle characters from 'Product_Code' starting at position 5 for 3 characters into a new column named 'Product_Number'.","Range of Characters","Add Column → Extract → Range → Starting Index: 5, Number of Characters: 3 → New column: Product_Number","001","Extracting order numbers, SKU components"</t>
-  </si>
-  <si>
-    <t>4,"Extract the text before the '@' symbol from 'Email_Address' into a new column named 'Username'. What is the username for john.smith@email.com?","Text Before Delimiter","Add Column → Extract → Text Before Delimiter → Delimiter: '@' → New column: Username","john.smith","Extracting usernames from emails, splitting email addresses"</t>
-  </si>
-  <si>
-    <t>5,"Extract the text after the '@' symbol from 'Email_Address' into a new column named 'Email_Domain'. What is the domain for john.smith@email.com?","Text After Delimiter","Add Column → Extract → Text After Delimiter → Delimiter: '@' → New column: Email_Domain","email.com","Extracting domain names, email provider analysis"</t>
-  </si>
-  <si>
-    <t>6,"Extract the area code from 'Phone_Number' column. For (555) 123-4567, extract the numbers between parentheses.","Text Between Delimiters","Add Column → Extract → Text Between Delimiters → Start: '(' , End: ')' → New column: Area_Code","555","Extracting area codes, phone number parsing"</t>
-  </si>
-  <si>
-    <t>7,"Extract the first 2 characters from 'Order_Reference' column. What is the prefix for ORD-1001-USA?","First Characters","Add Column → Extract → First Characters → Count: 2 → New column: Order_Prefix","OR","Identifying order types, document prefixes"</t>
-  </si>
-  <si>
-    <t>8,"Extract the last 3 characters from 'Order_Reference' column. What is the country code for ORD-1001-USA?","Last Characters","Add Column → Extract → Last Characters → Count: 3 → New column: Country_Code","USA","Extracting country codes, location identifiers"</t>
-  </si>
-  <si>
-    <t>9,"Extract the year from 'Date_Time_Stamp' column using the Year extraction. What is the year for 2024-01-05 14:30:00?","Date Year","Add Column → Date → Year → Select Date_Time_Stamp column","2024","Time intelligence, date part extraction"</t>
-  </si>
-  <si>
-    <t>10,"Extract the month name from 'Date_Time_Stamp' column. What is the month for the first record?","Date Month Name","Add Column → Date → Month → Name → Select Date_Time_Stamp column","January","Month analysis, seasonal reporting"</t>
-  </si>
-  <si>
-    <t>11,"Extract the day of week from 'Date_Time_Stamp' column. What day is 2024-01-05?","Date Day of Week","Add Column → Date → Day → Day of Week → Select Date_Time_Stamp column","Friday","Day-based analysis, weekday vs weekend trends"</t>
-  </si>
-  <si>
-    <t>12,"Extract the file name from 'File_Path' column (text after the last backslash). What is the file name for C:\Data\Sales\2024\Q1\January\report.csv?","Text After Last Delimiter","Add Column → Extract → Text After Delimiter → Delimiter: '\' → Select 'End of Delimiter' → New column: File_Name","report.csv","File parsing, path manipulation"</t>
-  </si>
-  <si>
-    <t>13,"Extract the folder name (second last segment) from 'File_Path' column. For C:\Data\Sales\2024\Q1\January\report.csv, extract 'January'.","Text Between Delimiters (Positional)","Split column by delimiter → Keep position 2 from end","January","Directory structure analysis, folder extraction"</t>
-  </si>
-  <si>
-    <t>14,"Extract the domain from 'URL' column (text between 'https://www.' and the next '/'). What is the domain for https://www.example.com/products/macbook-pro?","Text Between Delimiters","Add Column → Extract → Text Between Delimiters → Start: 'https://www.' → End: '/'","example.com","URL parsing, website analysis"</t>
-  </si>
-  <si>
-    <t>15,"Extract the product name from 'URL' column (text after the last '/'). What is the product for https://www.example.com/products/macbook-pro?","Text After Last Delimiter","Add Column → Extract → Text After Delimiter → Delimiter: '/' → Select 'End of Delimiter' → New column: Product_URL","macbook-pro","URL path extraction, slug analysis"</t>
-  </si>
-  <si>
-    <t>16,"Extract the first 5 characters from 'ID_Number' column. What is the prefix for ID-12345-ABCD?","First Characters","Add Column → Extract → First Characters → Count: 5 → New column: ID_Prefix","ID-12","ID type identification, prefix analysis"</t>
-  </si>
-  <si>
-    <t>17,"Extract the last 4 characters from 'ID_Number' column. What is the suffix for ID-12345-ABCD?","Last Characters","Add Column → Extract → Last Characters → Count: 4 → New column: ID_Suffix","ABCD","Suffix extraction, code analysis"</t>
-  </si>
-  <si>
-    <t>18,"Extract the serial number from 'Serial_Number' column (text after 'S/N:'). What is the serial number for S/N:MPR-2024-001?","Text After Delimiter","Add Column → Extract → Text After Delimiter → Delimiter: 'S/N:' → New column: Serial_Only","MPR-2024-001","Serial number extraction, product identification"</t>
-  </si>
-  <si>
-    <t>19,"Split 'Transaction_Code' by delimiter '|' into multiple columns. Then extract the quarter from the resulting columns.","Split Column + Extraction","Split Column → By Delimiter → '|' → Extract month column → Determine quarter","Q1 for month 01","Complex data parsing, transaction analysis"</t>
-  </si>
-  <si>
-    <t>20,"Extract the first word from 'Product_Name' column. What is the first word for 'MacBook Pro 16-inch'?","First Word","Add Column → Extract → First Characters based on space → Or split by space and take first","MacBook","Product name parsing, brand extraction"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -184,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,260 +316,788 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Product_Code,Order_Reference,Email_Address,Phone_Number,Product_Name,Address_Full,Date_Time_Stamp,File_Path,URL,ID_Number,Serial_Number,Transaction_Code</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,PRD-001-2024,ORD-1001-USA,john.smith@email.com,(555) 123-4567,MacBook Pro 16-inch,123 Main Street, Chicago IL 60601,2024-01-05 14:30:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/macbook-pro,ID-12345-ABCD,S/N:MPR-2024-001,TRX|2024|01|001</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,PRD-002-2024,ORD-1002-USA,jane.doe@company.com,(555) 234-5678,Magic Mouse Wireless,456 Oak Avenue, Boston MA 02101,2024-01-05 14:35:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/magic-mouse,ID-12346-EFGH,S/N:MMW-2024-002,TRX|2024|01|002</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,PRD-003-2024,ORD-1003-CAN,robert.wilson@email.ca,(555) 345-6789,Designer Jeans Blue,789 Pine Street, Toronto ON M5V 2T6,2024-01-06 09:15:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/designer-jeans,ID-12347-IJKL,S/N:DJB-2024-003,TRX|2024|01|003</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,PRD-004-2024,ORD-1004-USA,sarah.johnson@email.com,(555) 456-7890,27-inch 4K Monitor,321 Elm Street, Austin TX 78701,2024-01-06 10:45:00,C:\Data\Sales\2024\Q1\January\report.csv,https://www.example.com/products/4k-monitor,ID-12348-MNOP,S/N:4KM-2024-004,TRX|2024|01|004</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,PRD-005-2024,ORD-1005-UK,michael.brown@email.co.uk,44-20-7946-0123,Executive Leather Chair,654 Maple Avenue, London EC1A 1BB,2024-01-07 11:20:00,D:\Reports\2024\Q1\February\sales.csv,https://www.example.com/products/executive-chair,ID-12349-QRST,S/N:ELC-2024-005,TRX|2024|02|001</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,PRD-006-2024,ORD-1006-AUS,emily.davis@email.com.au,61-2-9876-5432,Mechanical RGB Keyboard,987 Cedar Lane, Sydney NSW 2000,2024-01-07 13:00:00,D:\Reports\2024\Q1\February\sales.csv,https://www.example.com/products/mechanical-keyboard,ID-12350-UVWX,S/N:MRK-2024-006,TRX|2024|02|002</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,PRD-007-2024,ORD-1007-USA,lisa.anderson@email.com,555-987-6543,Leather Jacket Black,147 Birch Street, Los Angeles CA 90001,2024-01-08 08:45:00,D:\Reports\2024\Q1\February\sales.csv,https://www.example.com/products/leather-jacket,ID-12351-YZAB,S/N:LJB-2024-007,TRX|2024|02|003</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,PRD-008-2024,ORD-1008-GER,robert.taylor@email.de,49-30-12345678,iPad Pro 12.9-inch,258 Spruce Avenue, Berlin 10115,2024-01-08 09:30:00,E:\Data\2024\March\products.csv,https://www.example.com/products/ipad-pro,ID-12352-CDEF,S/N:IPP-2024-008,TRX|2024|03|001</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,PRD-009-2024,ORD-1009-FRA,jennifer.martinez@email.fr,33-1-45678901,Floor Lamp Modern,369 Walnut Street, Paris 75001,2024-01-09 10:15:00,E:\Data\2024\March\products.csv,https://www.example.com/products/floor-lamp,ID-12353-GHIJ,S/N:FLM-2024-009,TRX|2024|03|002</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,PRD-010-2024,ORD-1010-USA,william.brown@email.com,555-321-0987,Running Shoes Pro,741 Cherry Lane, Detroit MI 48201,2024-01-09 14:20:00,E:\Data\2024\March\products.csv,https://www.example.com/products/running-shoes,ID-12354-KLMN,S/N:RSP-2024-010,TRX|2024|03|003</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,PRD-011-2024,ORD-1011-CAN,patricia.davis@email.ca,416-555-1234,Gaming Laptop RTX,852 Dogwood Drive, Vancouver BC V6B 4Y8,2024-01-10 11:00:00,F:\Sales\2024\April\transactions.csv,https://www.example.com/products/gaming-laptop,ID-12355-OPQR,S/N:GLP-2024-011,TRX|2024|04|001</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,PRD-012-2024,ORD-1012-UK,michael.miller@email.co.uk,44-141-555-6789,Wireless Noise Cancelling Headphones,951 Fir Lane, Manchester M1 1AE,2024-01-10 15:30:00,F:\Sales\2024\April\transactions.csv,https://www.example.com/products/headphones,ID-12356-STUV,S/N:WNC-2024-012,TRX|2024|04|002</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,PRD-013-2024,ORD-1013-USA,jessica.thomas@email.com,555-789-0123,Wool Winter Coat,753 Poplar Avenue, San Diego CA 92101,2024-01-11 09:45:00,F:\Sales\2024\April\transactions.csv,https://www.example.com/products/wool-coat,ID-12357-WXYZ,S/N:WWC-2024-013,TRX|2024|04|003</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,PRD-014-2024,ORD-1014-AUS,richard.moore@email.com.au,61-3-9876-5432,5-Tier Oak Bookshelf,159 Cypress Court, Melbourne VIC 3000,2024-01-11 12:15:00,G:\Data\2024\May\orders.csv,https://www.example.com/products/bookshelf,ID-12358-ABCD,S/N:BOO-2024-014,TRX|2024|05|001</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,PRD-015-2024,ORD-1015-GER,susan.taylor@email.de,49-89-1234567,Smartphone Pro Max,357 Willow Drive, Munich 80331,2024-01-12 10:00:00,G:\Data\2024\May\orders.csv,https://www.example.com/products/smartphone,ID-12359-EFGH,S/N:SPM-2024-015,TRX|2024|05|002</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,PRD-016-2024,ORD-1016-FRA,thomas.anderson@email.fr,33-4-98765432,Dress Shirt Formal White,951 Magnolia Road, Lyon 69001,2024-01-12 13:45:00,G:\Data\2024\May\orders.csv,https://www.example.com/products/dress-shirt,ID-12360-IJKL,S/N:DSF-2024-016,TRX|2024|05|003</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,PRD-017-2024,ORD-1017-USA,charles.jackson@email.com,555-456-7890,External SSD 1TB,753 Ash Street, Portland OR 97201,2024-01-13 08:30:00,H:\Reports\2024\June\inventory.csv,https://www.example.com/products/external-ssd,ID-12361-MNOP,S/N:ESS-2024-017,TRX|2024|06|001</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,PRD-018-2024,ORD-1018-CAN,sarah.white@email.ca,604-555-6789,Cotton Hoodie Gray,159 Beech Court, Calgary AB T2P 1J9,2024-01-13 16:20:00,H:\Reports\2024\June\inventory.csv,https://www.example.com/products/hoodie,ID-12362-QRST,S/N:CHG-2024-018,TRX|2024|06|002</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,PRD-019-2024,ORD-1019-UK,james.walker@email.co.uk,44-161-555-1234,Gaming Desk RGB,357 Cedar Avenue, Birmingham B1 1BB,2024-01-14 11:30:00,H:\Reports\2024\June\inventory.csv,https://www.example.com/products/gaming-desk,ID-12363-UVWX,S/N:GDR-2024-019,TRX|2024|06|003</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,PRD-020-2024,ORD-1020-USA,betty.hall@email.com,555-234-5678,4K Webcam Pro,753 Palm Avenue, Seattle WA 98101,2024-01-14 14:15:00,I:\Data\2024\July\products.csv,https://www.example.com/products/webcam,ID-12364-YZAB,S/N:4KW-2024-020,TRX|2024|07|001</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,PRD-021-2024,ORD-1021-AUS,kevin.young@email.com.au,61-7-5555-1234,Thunderbolt Docking Station,951 Elm Drive, Brisbane QLD 4000,2024-02-01 09:00:00,I:\Data\2024\July\products.csv,https://www.example.com/products/docking-station,ID-12365-CDEF,S/N:TDS-2024-021,TRX|2024|07|002</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,PRD-022-2024,ORD-1022-GER,nancy.allen@email.de,49-40-1234567,Winter Parka Black,753 Oak Court, Hamburg 20095,2024-02-01 10:45:00,I:\Data\2024\July\products.csv,https://www.example.com/products/winter-parka,ID-12366-GHIJ,S/N:WPB-2024-022,TRX|2024|07|003</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,PRD-023-2024,ORD-1023-FRA,edward.king@email.fr,33-5-98765432,Office Desk Walnut,159 Pine Street, Toulouse 31000,2024-02-02 13:30:00,J:\Sales\2024\August\transactions.csv,https://www.example.com/products/office-desk,ID-12367-KLMN,S/N:ODW-2024-023,TRX|2024|08|001</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,PRD-024-2024,ORD-1024-USA,donna.wright@email.com,555-876-5432,USB-C Hub 7-in-1,357 Spruce Lane, Denver CO 80201,2024-02-02 15:20:00,J:\Sales\2024\August\transactions.csv,https://www.example.com/products/usb-hub,ID-12368-OPQR,S/N:UCH-2024-024,TRX|2024|08|002</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,PRD-025-2024,ORD-1025-CAN,george.lopez@email.ca,403-555-9876,Casual Blazer Navy,951 Walnut Avenue, Edmonton AB T5J 0A9,2024-02-03 08:15:00,J:\Sales\2024\August\transactions.csv,https://www.example.com/products/casual-blazer,ID-12369-STUV,S/N:CBN-2024-025,TRX|2024|08|003</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Extract the first 3 characters from 'Product_Code' column into a new column named 'Product_Prefix'. What is the prefix for the first product?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Extract the last 4 characters from 'Product_Code' column into a new column named 'Product_Year'. What is the year for the first product?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Extract the middle characters from 'Product_Code' starting at position 5 for 3 characters into a new column named 'Product_Number'.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Extract the text before the '@' symbol from 'Email_Address' into a new column named 'Username'. What is the username for john.smith@email.com?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Extract the text after the '@' symbol from 'Email_Address' into a new column named 'Email_Domain'. What is the domain for john.smith@email.com?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Extract the area code from 'Phone_Number' column. For (555) 123-4567, extract the numbers between parentheses.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Extract the first 2 characters from 'Order_Reference' column. What is the prefix for ORD-1001-USA?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Extract the last 3 characters from 'Order_Reference' column. What is the country code for ORD-1001-USA?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Extract the year from 'Date_Time_Stamp' column using the Year extraction. What is the year for 2024-01-05 14:30:00?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Extract the month name from 'Date_Time_Stamp' column. What is the month for the first record?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Extract the day of week from 'Date_Time_Stamp' column. What day is 2024-01-05?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Extract the file name from 'File_Path' column (text after the last backslash). What is the file name for C:\Data\Sales\2024\Q1\January\report.csv?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Extract the folder name (second last segment) from 'File_Path' column. For C:\Data\Sales\2024\Q1\January\report.csv, extract 'January'.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Extract the domain from 'URL' column (text between 'https://www.' and the next '/'). What is the domain for https://www.example.com/products/macbook-pro?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Extract the product name from 'URL' column (text after the last '/'). What is the product for https://www.example.com/products/macbook-pro?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Extract the first 5 characters from 'ID_Number' column. What is the prefix for ID-12345-ABCD?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Extract the last 4 characters from 'ID_Number' column. What is the suffix for ID-12345-ABCD?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Extract the serial number from 'Serial_Number' column (text after 'S/N:'). What is the serial number for S/N:MPR-2024-001?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Split 'Transaction_Code' by delimiter '|' into multiple columns. Then extract the quarter from the resulting columns.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Extracting Characters</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Extract the first word from 'Product_Name' column. What is the first word for 'MacBook Pro 16-inch'?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>